--- a/AAII_Financials/Quarterly/CMTG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CMTG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="92">
   <si>
     <t>CMTG</t>
   </si>
@@ -656,116 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
@@ -775,8 +776,11 @@
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -786,69 +790,69 @@
       <c r="E8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
         <v>12400</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>23700</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>23700</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3">
         <v>65100</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3">
         <v>33600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>66900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>176100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>144400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>146200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>97500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>113300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>112400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>110700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>106900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>105200</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
@@ -858,80 +862,83 @@
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E9" s="3">
         <v>18100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>21400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>102400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>77900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>56700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>49400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>10000</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
@@ -941,80 +948,83 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-208600</v>
+      </c>
+      <c r="E10" s="3">
         <v>-29100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-195300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-6100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-161700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-17200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-35500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-30300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>50600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-49500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>22300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>56900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>73700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>66500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>89500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>48100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>103300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>102600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>101000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>97300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>95200</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1024,8 +1034,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1055,8 +1068,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1138,8 +1152,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1221,52 +1238,55 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E14" s="3">
         <v>5900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-15000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>43200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>88300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-2200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
@@ -1280,8 +1300,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1304,28 +1324,31 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E15" s="3">
         <v>6400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>400</v>
-      </c>
-      <c r="I15" s="3">
-        <v>2600</v>
       </c>
       <c r="J15" s="3">
         <v>2600</v>
@@ -1343,40 +1366,40 @@
         <v>2600</v>
       </c>
       <c r="O15" s="3">
-        <v>2100</v>
+        <v>2600</v>
       </c>
       <c r="P15" s="3">
         <v>2100</v>
       </c>
       <c r="Q15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="R15" s="3">
         <v>2000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1900</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y15" s="3">
         <v>1300</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>0</v>
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
@@ -1387,8 +1410,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1415,80 +1441,81 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E17" s="3">
         <v>37300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>43000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>36900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>34500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>31100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>36100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>35100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>34200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>33100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>30500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>33700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>30700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>31800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>196300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>102000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>83100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>65600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>45100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>11500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>62300</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1498,80 +1525,83 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-228100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-48400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-217000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-24500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-180600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-35400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-12300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-55900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-50500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>34700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-69500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>35100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-20200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>42400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>63100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>31900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>68200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>100900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>97000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>100800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>42900</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1581,8 +1611,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1612,13 +1645,14 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-1900</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1645,47 +1679,47 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2800</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-5200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-6000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-500</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1695,68 +1729,71 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-220000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-42000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-211300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-20800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-179700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-35000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-53300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-48000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>36600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-67000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>38700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-15700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>48200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>67900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>33900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>65000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1778,8 +1815,11 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1822,33 +1862,33 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3">
         <v>5000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>40000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>42800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>50900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>47800</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1861,80 +1901,83 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-255400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-54300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-219200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-181700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-78600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-100700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-56200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-52800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>34000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-68900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>36700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-22700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>42200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>63200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>29400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>23000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>52800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>40100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>54400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>42400</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1944,8 +1987,11 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1991,8 +2037,8 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -2001,25 +2047,25 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>6000</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>-1800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB24" s="3">
         <v>0</v>
@@ -2027,8 +2073,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2110,80 +2159,83 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-255400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-54300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-219200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-181700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-78600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-100700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-56200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-52800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>34000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-68900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>36700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-22700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>42200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>63200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>29400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>17000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>52800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>42000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>58600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>42400</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2193,80 +2245,83 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-255400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-54300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-219200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-181700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-78600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-100700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-56500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-53700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>33400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-69600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>35500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-23500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>41300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>62400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>29400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>17000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>52900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>42000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>58600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>43200</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2276,8 +2331,11 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2359,8 +2417,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2442,8 +2503,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2525,8 +2589,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2608,13 +2675,16 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2641,47 +2711,47 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2800</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>5200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>6000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>500</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,80 +2761,83 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-255400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-54300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-219200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-181700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-78600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-100700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-56200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-52800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>34000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-68900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>36700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-23500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>41300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>62400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>29400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>17000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>52900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>42000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>58600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>43200</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2774,8 +2847,11 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2857,80 +2933,83 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-255400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-54300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-219200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-181700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-78600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-100700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-56200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-52800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>34000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-68900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>36700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-23500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>41300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>62400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>29400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>17000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>52900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>42000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>58600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>43200</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2940,85 +3019,88 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3028,8 +3110,11 @@
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3059,8 +3144,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3090,71 +3176,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>90300</v>
+      </c>
+      <c r="E41" s="3">
         <v>116800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>173200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>339500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>209200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>127800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>99100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>113900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>148200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>232500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>187300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>307400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>253100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>426500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>306500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>225600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>461000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>444000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>310200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>235600</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,8 +3260,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3200,26 +3290,26 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4600</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -3256,71 +3346,74 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2790300</v>
+      </c>
+      <c r="E43" s="3">
         <v>3107600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3615400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4213200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4881400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5738700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5947300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6142700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6709500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6635300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6888400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7014200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7417000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7483900</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U43" s="3">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3">
         <v>26000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>30300</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3339,8 +3432,11 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3383,8 +3479,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3422,13 +3518,16 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>75300</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -3436,8 +3535,8 @@
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
-        <v>307000</v>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
         <v>307000</v>
@@ -3445,8 +3544,8 @@
       <c r="I45" s="3">
         <v>307000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+      <c r="J45" s="3">
+        <v>307000</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -3466,8 +3565,8 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -3505,53 +3604,56 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3037700</v>
+      </c>
+      <c r="E46" s="3">
         <v>3238000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3806200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4597500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5416400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6340200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6664800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6611300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6879200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7059600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7365900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7347500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7706500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7954600</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3588,13 +3690,16 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>42200</v>
+        <v>42100</v>
       </c>
       <c r="E47" s="3">
         <v>42200</v>
@@ -3603,7 +3708,7 @@
         <v>42200</v>
       </c>
       <c r="G47" s="3">
-        <v>42300</v>
+        <v>42200</v>
       </c>
       <c r="H47" s="3">
         <v>42300</v>
@@ -3612,7 +3717,7 @@
         <v>42300</v>
       </c>
       <c r="J47" s="3">
-        <v>42400</v>
+        <v>42300</v>
       </c>
       <c r="K47" s="3">
         <v>42400</v>
@@ -3621,7 +3726,7 @@
         <v>42400</v>
       </c>
       <c r="M47" s="3">
-        <v>42500</v>
+        <v>42400</v>
       </c>
       <c r="N47" s="3">
         <v>42500</v>
@@ -3630,29 +3735,29 @@
         <v>42500</v>
       </c>
       <c r="P47" s="3">
+        <v>42500</v>
+      </c>
+      <c r="Q47" s="3">
         <v>43400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7402300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7318600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7052400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7135900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6656700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>6614000</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3671,53 +3776,56 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>647300</v>
+      </c>
+      <c r="E48" s="3">
         <v>764800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>730000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>661600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>218500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>126900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>127100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>516400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>518700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>521000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>523000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>520500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>522400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>399800</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
-      </c>
       <c r="R48" s="3">
         <v>0</v>
       </c>
@@ -3754,32 +3862,35 @@
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E49" s="3">
         <v>18200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>19800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>21600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>20400</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
@@ -3787,22 +3898,22 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>23000</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>24300</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -3837,8 +3948,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3920,8 +4034,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4003,71 +4120,74 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>106900</v>
+      </c>
+      <c r="E52" s="3">
         <v>101200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>123600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>118200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>124300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>127100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>112300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>138000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>144200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>132700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>115000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>137900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>104800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>86600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>41700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>37100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>36700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>23100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>43500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>42600</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4086,8 +4206,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4169,71 +4292,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3835400</v>
+      </c>
+      <c r="E54" s="3">
         <v>4164400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4721800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5441500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5823100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6656200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6967000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7308100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7584600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7755800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8069400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8048400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8400600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8484400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8241500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8057900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8016200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8072800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7455300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7352300</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4252,8 +4378,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4283,8 +4412,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4314,8 +4444,9 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4358,8 +4489,8 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -4367,18 +4498,18 @@
       <c r="S57" s="3">
         <v>0</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U57" s="3">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3">
         <v>46200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>32700</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4397,13 +4528,16 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>650000</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -4415,53 +4549,53 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>275200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>274600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>279700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>827800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>277600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>289900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>289800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>542600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2499200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5110800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4855100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4755000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4902400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4277300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3885500</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4480,8 +4614,11 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4503,48 +4640,48 @@
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>14200</v>
-      </c>
-      <c r="K59" s="3">
-        <v>136300</v>
       </c>
       <c r="L59" s="3">
         <v>136300</v>
       </c>
       <c r="M59" s="3">
+        <v>136300</v>
+      </c>
+      <c r="N59" s="3">
         <v>135800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>163700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>190700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>296500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>121100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>114700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>107500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>133400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>70000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>76400</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4563,53 +4700,56 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>658100</v>
+      </c>
+      <c r="E60" s="3">
         <v>8000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>284300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>304700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>313900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>974100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>423700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>436100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>464000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>744000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2807600</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -4646,71 +4786,74 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1916100</v>
+      </c>
+      <c r="E61" s="3">
         <v>2629600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3145000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3645900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4019500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4400600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4614500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4851000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4396900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5072500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5267000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5104900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5069500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3155300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>553200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>552900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>563300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>457700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>457600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>814300</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4729,53 +4872,56 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E62" s="3">
         <v>34000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>36100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>38100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>37400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>36700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>39600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>39200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>42200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>43700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>66400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>182900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>186700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>77300</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -4812,8 +4958,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4895,8 +5044,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4978,8 +5130,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5061,71 +5216,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2597400</v>
+      </c>
+      <c r="E66" s="3">
         <v>2671600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3189900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3692700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4066100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4721600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4958900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5204100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5413200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5539900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5769500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5751800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6000200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6040300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5785000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5522700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5464300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5531700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4888600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4983300</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5144,8 +5302,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5175,8 +5336,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5258,8 +5420,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5341,8 +5506,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5401,11 +5569,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>100</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5424,8 +5592,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5507,71 +5678,74 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1532100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1276700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1222400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1003200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-993700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-811900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-733300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-632600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-562200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-515100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-426700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-425400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-321100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-273000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-257200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>799400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>757300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>694100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>664700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>597300</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5590,8 +5764,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5673,8 +5850,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5756,8 +5936,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5839,71 +6022,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1238000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1492800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1531900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1748800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1757000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1934600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2008100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2104000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2171400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2215900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2299900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2296700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2400400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2444200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2456500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2535200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2552000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2541200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2566600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2368800</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5922,8 +6108,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6005,85 +6194,88 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6093,80 +6285,83 @@
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-255400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-54300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-219200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-181700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-78600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-100700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-56200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-52800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>34000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-68900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>36700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-23500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>41300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>62400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>29400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>17000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>52900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>42000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>58600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>43200</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6176,8 +6371,11 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6207,67 +6405,68 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>400</v>
+      </c>
+      <c r="E83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2600</v>
-      </c>
-      <c r="K83" s="3">
-        <v>2100</v>
       </c>
       <c r="L83" s="3">
         <v>2100</v>
       </c>
       <c r="M83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N83" s="3">
         <v>2000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>1900</v>
       </c>
       <c r="U83" s="3">
         <v>1900</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>1900</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
@@ -6281,8 +6480,8 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -6290,8 +6489,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6373,8 +6575,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6456,8 +6661,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6539,8 +6747,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6622,8 +6833,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6705,80 +6919,83 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-35800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>18300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>39200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>21500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>27300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>41900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>22400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>19500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>20000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>18900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>49500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>22600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>69000</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z89" s="3">
         <v>140500</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6788,8 +7005,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6819,8 +7039,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6863,32 +7084,32 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9700</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -6902,8 +7123,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6985,8 +7209,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7068,80 +7295,83 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E94" s="3">
         <v>400500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>338600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>505100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>749200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>274800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>233100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>179700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>80400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>286600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-131800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>296600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-106500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-97600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-122400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-278400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>84100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-456600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-70700</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-208900</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7151,8 +7381,11 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7182,8 +7415,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7202,33 +7436,33 @@
       <c r="H96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3">
         <v>14200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>35500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>35600</v>
-      </c>
-      <c r="L96" s="3">
-        <v>35300</v>
       </c>
       <c r="M96" s="3">
         <v>35300</v>
       </c>
       <c r="N96" s="3">
-        <v>52400</v>
+        <v>35300</v>
       </c>
       <c r="O96" s="3">
         <v>52400</v>
       </c>
       <c r="P96" s="3">
+        <v>52400</v>
+      </c>
+      <c r="Q96" s="3">
         <v>52000</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -7251,11 +7485,11 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-12400</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -7265,8 +7499,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7348,8 +7585,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7431,8 +7671,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7514,80 +7757,83 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-67500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-454400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-506500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-385500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-664300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-223600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-262300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-243900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-168300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-271200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-11200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-293000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-96900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>196100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>187900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>24400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-103000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>567000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>76000</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z100" s="3">
         <v>161300</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7597,8 +7843,11 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7641,8 +7890,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -7680,80 +7929,83 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-60300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-165500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>128300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>79000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>15400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-25000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-82400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>36900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-115700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>45500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-181000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>117900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>85500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-235100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>30600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>133000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>74300</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3">
         <v>93000</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7761,6 +8013,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
